--- a/基础规则说明书.xlsx
+++ b/基础规则说明书.xlsx
@@ -5,18 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\energy-duel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11411\Desktop\file\工程\energy-duel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976CB863-6C88-47B5-B8E0-50A5973EEE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BE8FBA-7A75-41E2-81B9-5BED9868FF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="3975" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="23040" windowHeight="12120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="184">
   <si>
     <t>娇斯拉大战贡刚</t>
   </si>
@@ -435,13 +440,199 @@
   <si>
     <t>锻造0.5并激活君王之剑</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皮卡丘</t>
+  </si>
+  <si>
+    <t>设计理念</t>
+  </si>
+  <si>
+    <t>十伯伏特</t>
+  </si>
+  <si>
+    <t>1蓄力</t>
+  </si>
+  <si>
+    <t>以自身为中心沿两侧地块依次传导造成伤害</t>
+  </si>
+  <si>
+    <t>最初的群攻技能英雄，加入位移是为了更快引入移动和地块机制，以及如果多人战斗会发现，只有两侧的对手承受压力，而其他的人甚至会出现攻击不到的现象</t>
+  </si>
+  <si>
+    <t>十万伏特</t>
+  </si>
+  <si>
+    <t>2气2蓄力</t>
+  </si>
+  <si>
+    <t>同上</t>
+  </si>
+  <si>
+    <t>迅雷</t>
+  </si>
+  <si>
+    <t>位移</t>
+  </si>
+  <si>
+    <t>使用后的下一个十伯伏特可不消耗资源释放</t>
+  </si>
+  <si>
+    <t>李淳罡</t>
+  </si>
+  <si>
+    <t>剑道</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>被动</t>
+  </si>
+  <si>
+    <t>李淳罡无法使用“拳”，“斩”的消耗降低2/3</t>
+  </si>
+  <si>
+    <t>引入被动技能，优化其技能描述，为了将来可能存在的机制做准备</t>
+  </si>
+  <si>
+    <t>剑气</t>
+  </si>
+  <si>
+    <t>可后置选择一个目标并对其进行斩击</t>
+  </si>
+  <si>
+    <t>一剑开天门</t>
+  </si>
+  <si>
+    <t>吸</t>
+  </si>
+  <si>
+    <t>目标如使用“蓄力”，将其抢夺，同时全场人员获得技能“削”</t>
+  </si>
+  <si>
+    <t>将以前所有类似角色进行整合与精简的版本</t>
+  </si>
+  <si>
+    <t>熟能生巧</t>
+  </si>
+  <si>
+    <t>每次获取资源成功时，会将“凹”与“吸”进行升级，依次获得如下效果：1，获得0.5的等级。2，可以后置选择。3，获得1的等级。4，可造成伤害</t>
+  </si>
+  <si>
+    <t>凹凹神功</t>
+  </si>
+  <si>
+    <t>5任意资源</t>
+  </si>
+  <si>
+    <t>2.5＋0.5n</t>
+  </si>
+  <si>
+    <t>n为“熟能生巧”中获得的效果数量。每次通过“熟能生巧”升级时，资源所消耗数-n，使用后重置</t>
+  </si>
+  <si>
+    <t>削</t>
+  </si>
+  <si>
+    <t>无效全场所有人的“吸”，并左移其血量</t>
+  </si>
+  <si>
+    <t>梦魇</t>
+  </si>
+  <si>
+    <t>暗影之刃</t>
+  </si>
+  <si>
+    <t>无法使用“拳”和“斩”，每四个回合可使用一次“暗影之刃”对以自己为中心的三个相邻地块造成等级为1.5，速度为2的范围斩击。开局拥有一次使用机会，每次释放招式回缩减一回合冷却</t>
+  </si>
+  <si>
+    <t>遵照了当年设定的lol类英雄，没有拳与斩，目标是一击制胜的击杀</t>
+  </si>
+  <si>
+    <t>魇之梦径</t>
+  </si>
+  <si>
+    <t>选择一个目标并沿顺时针方向铺设“魇之梦径”，对路径上的所有人造成魔法伤害，在路径上可以在回合结束后进行一次位移，且攻击等级加0.5.持续三回合</t>
+  </si>
+  <si>
+    <t>黑暗庇护</t>
+  </si>
+  <si>
+    <t>使用时可吸收攻击类招式，若吸收成功，则在之后三回合内速度加1，攻击力加0.5。在面对复数攻击时，只能抵挡最高等级的攻击。</t>
+  </si>
+  <si>
+    <t>无言恐惧</t>
+  </si>
+  <si>
+    <t>1气1蓄力</t>
+  </si>
+  <si>
+    <t>对一个指定目标使用后，如果对方招式等级小于等于该次攻击等级，则使其恐惧（本回合及下回合无法使用除“气”外的招式，且收到攻击等级加1）</t>
+  </si>
+  <si>
+    <t>鬼影重重</t>
+  </si>
+  <si>
+    <t>1气3蓄力</t>
+  </si>
+  <si>
+    <t>全场陷入黑暗（其他玩家无法知道除本地块外的状态变化以及招式）两回合（包括本回合），并在期间可对目标进行锁定攻击，如直接击杀目标，则位移至该目标所在地块，如未击杀，则位于目标顺时针方向一格地块</t>
+  </si>
+  <si>
+    <t>泥岩</t>
+  </si>
+  <si>
+    <t>土石之子</t>
+  </si>
+  <si>
+    <t>无“斩”，“拳”无脆弱，但使用时受到等级差≥0.5的伤害时将直接死亡；每次使用“拳”会使泥岩的“拳”等级永久+0.5</t>
+  </si>
+  <si>
+    <t>沃土予身</t>
+  </si>
+  <si>
+    <t>无屏障状态下，每隔3回合，在第4回合获得一层屏障，失去屏障时右移一次自己的状态</t>
+  </si>
+  <si>
+    <t>变身当回合参与回合计数</t>
+  </si>
+  <si>
+    <t>屏障上限为1</t>
+  </si>
+  <si>
+    <t>岩崩锤</t>
+  </si>
+  <si>
+    <t>常态无法使用，每被他人选中3次获得一次使用次数</t>
+  </si>
+  <si>
+    <t>对以自身为中心，左右各2地块范围内的所有敌人造成钝击伤害并右移一次自己的状态</t>
+  </si>
+  <si>
+    <t>状态右移的效果速度为4</t>
+  </si>
+  <si>
+    <t>秽壤的血脉</t>
+  </si>
+  <si>
+    <t>3气</t>
+  </si>
+  <si>
+    <t>使用后的当回合及下2回合进入沉睡状态，苏醒时获得“斩”，且每沉睡1回合，攻击等级+0.5，持续沉睡回合数</t>
+  </si>
+  <si>
+    <t>沉睡期间可主动退出沉睡状态并使用技能，返还等同于未沉睡回合数的资源</t>
+  </si>
+  <si>
+    <t>沉睡：持续期间无法被选中并免疫伤害</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -491,6 +682,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -500,7 +706,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -560,11 +766,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -584,14 +827,8 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -602,6 +839,15 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -611,7 +857,58 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -932,24 +1229,24 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:V201"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="22" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -963,7 +1260,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -987,7 +1284,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -1003,18 +1300,18 @@
       <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="9"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="13"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -1023,7 +1320,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -1059,7 +1356,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1095,7 +1392,7 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
@@ -1135,7 +1432,7 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -1173,7 +1470,7 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
@@ -1192,13 +1489,13 @@
       <c r="F8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
@@ -1211,7 +1508,7 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>24</v>
       </c>
@@ -1230,12 +1527,12 @@
       <c r="F9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="9"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -1249,7 +1546,7 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>26</v>
       </c>
@@ -1271,16 +1568,16 @@
       <c r="G10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="9"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="13"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1289,7 +1586,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1308,12 +1605,12 @@
       <c r="F11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -1327,7 +1624,7 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>31</v>
       </c>
@@ -1363,7 +1660,7 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
@@ -1382,10 +1679,10 @@
       <c r="F13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="9"/>
+      <c r="H13" s="13"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -1401,7 +1698,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
@@ -1417,12 +1714,12 @@
       <c r="E14" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="9"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="13"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
@@ -1437,7 +1734,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1461,7 +1758,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1485,7 +1782,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1509,7 +1806,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
-    <row r="18" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1533,7 +1830,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
-    <row r="19" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1557,7 +1854,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
     </row>
-    <row r="20" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1581,7 +1878,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
     </row>
-    <row r="21" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1605,7 +1902,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
     </row>
-    <row r="22" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1629,7 +1926,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1653,7 +1950,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1677,7 +1974,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1701,7 +1998,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="2"/>
@@ -1725,18 +2022,18 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="1"/>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1753,72 +2050,72 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
+    <row r="28" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="11" t="s">
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="2"/>
     </row>
-    <row r="29" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
+    <row r="29" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
       <c r="B29" s="3"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="11" t="s">
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11" t="s">
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="9"/>
+      <c r="C30" s="13"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -1839,19 +2136,19 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
     </row>
-    <row r="31" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="13"/>
       <c r="I31" s="6"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1867,19 +2164,19 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
     </row>
-    <row r="32" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="13"/>
       <c r="I32" s="6"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1895,19 +2192,19 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
     </row>
-    <row r="33" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="13"/>
       <c r="I33" s="6"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1923,19 +2220,19 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
     </row>
-    <row r="34" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="9"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="13"/>
       <c r="I34" s="6"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1951,20 +2248,20 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
     </row>
-    <row r="35" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="9"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="13"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1979,7 +2276,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
     </row>
-    <row r="36" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2003,7 +2300,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
     </row>
-    <row r="37" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2027,7 +2324,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
     </row>
-    <row r="38" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2051,7 +2348,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
     </row>
-    <row r="39" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2075,7 +2372,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
     </row>
-    <row r="40" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2099,7 +2396,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
     </row>
-    <row r="41" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2123,7 +2420,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
     </row>
-    <row r="42" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2147,7 +2444,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
     </row>
-    <row r="43" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2171,7 +2468,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
     </row>
-    <row r="44" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2195,7 +2492,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
     </row>
-    <row r="45" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2219,7 +2516,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
     </row>
-    <row r="46" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2243,7 +2540,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
     </row>
-    <row r="47" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2267,7 +2564,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
     </row>
-    <row r="48" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2291,7 +2588,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
     </row>
-    <row r="49" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2315,7 +2612,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
     </row>
-    <row r="50" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2339,7 +2636,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
     </row>
-    <row r="51" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2363,7 +2660,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2387,7 +2684,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
     </row>
-    <row r="53" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2411,7 +2708,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
     </row>
-    <row r="54" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2435,7 +2732,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
     </row>
-    <row r="55" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2459,7 +2756,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
     </row>
-    <row r="56" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2483,7 +2780,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
     </row>
-    <row r="57" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2507,7 +2804,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
     </row>
-    <row r="58" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2531,7 +2828,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
     </row>
-    <row r="59" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2555,7 +2852,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
     </row>
-    <row r="60" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2579,7 +2876,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2603,7 +2900,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2627,7 +2924,7 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
     </row>
-    <row r="63" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2651,7 +2948,7 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
     </row>
-    <row r="64" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2675,7 +2972,7 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
     </row>
-    <row r="65" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2699,7 +2996,7 @@
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
     </row>
-    <row r="66" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2723,7 +3020,7 @@
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
     </row>
-    <row r="67" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2747,7 +3044,7 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
     </row>
-    <row r="68" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2771,7 +3068,7 @@
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
     </row>
-    <row r="69" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2795,7 +3092,7 @@
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
     </row>
-    <row r="70" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2819,7 +3116,7 @@
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
     </row>
-    <row r="71" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2843,7 +3140,7 @@
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
     </row>
-    <row r="72" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2867,7 +3164,7 @@
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2891,7 +3188,7 @@
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
     </row>
-    <row r="74" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2915,7 +3212,7 @@
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2939,7 +3236,7 @@
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
     </row>
-    <row r="76" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2963,7 +3260,7 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2987,7 +3284,7 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3011,7 +3308,7 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
     </row>
-    <row r="79" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3035,7 +3332,7 @@
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3059,7 +3356,7 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
     </row>
-    <row r="81" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3083,7 +3380,7 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3107,7 +3404,7 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3131,7 +3428,7 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3155,7 +3452,7 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3179,7 +3476,7 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3203,7 +3500,7 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3227,7 +3524,7 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3251,7 +3548,7 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3275,7 +3572,7 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3299,7 +3596,7 @@
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3323,7 +3620,7 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
     </row>
-    <row r="92" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3347,7 +3644,7 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
     </row>
-    <row r="93" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3371,7 +3668,7 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
     </row>
-    <row r="94" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3395,7 +3692,7 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
     </row>
-    <row r="95" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3419,7 +3716,7 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
     </row>
-    <row r="96" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3443,7 +3740,7 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
     </row>
-    <row r="97" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3467,7 +3764,7 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
     </row>
-    <row r="98" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3491,7 +3788,7 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
     </row>
-    <row r="99" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3515,7 +3812,7 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
     </row>
-    <row r="100" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3539,7 +3836,7 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
     </row>
-    <row r="101" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3563,7 +3860,7 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
     </row>
-    <row r="102" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3587,7 +3884,7 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
     </row>
-    <row r="103" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3611,7 +3908,7 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
     </row>
-    <row r="104" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3635,7 +3932,7 @@
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
     </row>
-    <row r="105" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3659,7 +3956,7 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
     </row>
-    <row r="106" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3683,7 +3980,7 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
     </row>
-    <row r="107" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3707,7 +4004,7 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
     </row>
-    <row r="108" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3731,7 +4028,7 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
     </row>
-    <row r="109" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3755,7 +4052,7 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
     </row>
-    <row r="110" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3779,7 +4076,7 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
     </row>
-    <row r="111" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3803,7 +4100,7 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
     </row>
-    <row r="112" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3827,7 +4124,7 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
     </row>
-    <row r="113" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3851,7 +4148,7 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
     </row>
-    <row r="114" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3875,7 +4172,7 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
     </row>
-    <row r="115" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3899,7 +4196,7 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
     </row>
-    <row r="116" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3923,7 +4220,7 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
     </row>
-    <row r="117" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3947,7 +4244,7 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
     </row>
-    <row r="118" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3971,7 +4268,7 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
     </row>
-    <row r="119" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3995,7 +4292,7 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
     </row>
-    <row r="120" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4019,7 +4316,7 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
     </row>
-    <row r="121" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4043,7 +4340,7 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
     </row>
-    <row r="122" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4067,7 +4364,7 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
     </row>
-    <row r="123" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4091,7 +4388,7 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
     </row>
-    <row r="124" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4115,7 +4412,7 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
     </row>
-    <row r="125" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4139,7 +4436,7 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
     </row>
-    <row r="126" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4163,7 +4460,7 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
     </row>
-    <row r="127" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4187,7 +4484,7 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
     </row>
-    <row r="128" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4211,7 +4508,7 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
     </row>
-    <row r="129" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4235,7 +4532,7 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
     </row>
-    <row r="130" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4259,7 +4556,7 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
     </row>
-    <row r="131" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4283,7 +4580,7 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
     </row>
-    <row r="132" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4307,7 +4604,7 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
     </row>
-    <row r="133" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4331,7 +4628,7 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
     </row>
-    <row r="134" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4355,7 +4652,7 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
     </row>
-    <row r="135" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4379,7 +4676,7 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
     </row>
-    <row r="136" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4403,7 +4700,7 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
     </row>
-    <row r="137" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4427,7 +4724,7 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
     </row>
-    <row r="138" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4451,7 +4748,7 @@
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
     </row>
-    <row r="139" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4475,7 +4772,7 @@
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
     </row>
-    <row r="140" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4499,7 +4796,7 @@
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
     </row>
-    <row r="141" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4523,7 +4820,7 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
     </row>
-    <row r="142" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4547,7 +4844,7 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
     </row>
-    <row r="143" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4571,7 +4868,7 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
     </row>
-    <row r="144" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4595,7 +4892,7 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
     </row>
-    <row r="145" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4619,7 +4916,7 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
     </row>
-    <row r="146" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4643,7 +4940,7 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
     </row>
-    <row r="147" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4667,7 +4964,7 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
     </row>
-    <row r="148" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4691,7 +4988,7 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
     </row>
-    <row r="149" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4715,7 +5012,7 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
     </row>
-    <row r="150" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4739,7 +5036,7 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
     </row>
-    <row r="151" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4763,7 +5060,7 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
     </row>
-    <row r="152" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4787,7 +5084,7 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
     </row>
-    <row r="153" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4811,7 +5108,7 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
     </row>
-    <row r="154" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4835,7 +5132,7 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
     </row>
-    <row r="155" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4859,7 +5156,7 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
     </row>
-    <row r="156" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4883,7 +5180,7 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
     </row>
-    <row r="157" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4907,7 +5204,7 @@
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
     </row>
-    <row r="158" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4931,7 +5228,7 @@
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
     </row>
-    <row r="159" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4955,7 +5252,7 @@
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
     </row>
-    <row r="160" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4979,7 +5276,7 @@
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
     </row>
-    <row r="161" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5003,7 +5300,7 @@
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
     </row>
-    <row r="162" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5027,7 +5324,7 @@
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
     </row>
-    <row r="163" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5051,7 +5348,7 @@
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
     </row>
-    <row r="164" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5075,7 +5372,7 @@
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
     </row>
-    <row r="165" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5099,7 +5396,7 @@
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
     </row>
-    <row r="166" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5123,7 +5420,7 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
     </row>
-    <row r="167" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5147,7 +5444,7 @@
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
     </row>
-    <row r="168" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5171,7 +5468,7 @@
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
     </row>
-    <row r="169" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5195,7 +5492,7 @@
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
     </row>
-    <row r="170" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5219,7 +5516,7 @@
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
     </row>
-    <row r="171" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5243,7 +5540,7 @@
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
     </row>
-    <row r="172" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5267,7 +5564,7 @@
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
     </row>
-    <row r="173" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5291,7 +5588,7 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
     </row>
-    <row r="174" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5315,7 +5612,7 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
     </row>
-    <row r="175" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5339,7 +5636,7 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
     </row>
-    <row r="176" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5363,7 +5660,7 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
     </row>
-    <row r="177" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5387,7 +5684,7 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
     </row>
-    <row r="178" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5411,7 +5708,7 @@
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
     </row>
-    <row r="179" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5435,7 +5732,7 @@
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
     </row>
-    <row r="180" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5459,7 +5756,7 @@
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
     </row>
-    <row r="181" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5483,7 +5780,7 @@
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
     </row>
-    <row r="182" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5507,7 +5804,7 @@
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
     </row>
-    <row r="183" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5531,7 +5828,7 @@
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
     </row>
-    <row r="184" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5555,7 +5852,7 @@
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
     </row>
-    <row r="185" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5579,7 +5876,7 @@
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
     </row>
-    <row r="186" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5603,7 +5900,7 @@
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
     </row>
-    <row r="187" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5627,7 +5924,7 @@
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
     </row>
-    <row r="188" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5651,7 +5948,7 @@
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
     </row>
-    <row r="189" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5675,7 +5972,7 @@
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
     </row>
-    <row r="190" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5699,7 +5996,7 @@
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
     </row>
-    <row r="191" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5723,7 +6020,7 @@
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
     </row>
-    <row r="192" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5747,7 +6044,7 @@
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
     </row>
-    <row r="193" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5771,7 +6068,7 @@
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
     </row>
-    <row r="194" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5795,7 +6092,7 @@
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
     </row>
-    <row r="195" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5819,7 +6116,7 @@
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
     </row>
-    <row r="196" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5843,7 +6140,7 @@
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
     </row>
-    <row r="197" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5867,7 +6164,7 @@
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
     </row>
-    <row r="198" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5891,7 +6188,7 @@
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
     </row>
-    <row r="199" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5915,7 +6212,7 @@
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
     </row>
-    <row r="200" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5939,7 +6236,7 @@
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
     </row>
-    <row r="201" spans="1:22" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:22" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5965,6 +6262,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="P29:R29"/>
     <mergeCell ref="M29:O29"/>
@@ -5979,12 +6282,6 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
@@ -6003,22 +6300,22 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:V200"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -6035,7 +6332,7 @@
       <c r="U1" s="5"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -6071,7 +6368,7 @@
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>50</v>
       </c>
@@ -6105,7 +6402,7 @@
       <c r="U3" s="5"/>
       <c r="V3" s="5"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -6129,7 +6426,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -6153,7 +6450,7 @@
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -6177,7 +6474,7 @@
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -6201,7 +6498,7 @@
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -6225,7 +6522,7 @@
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -6249,7 +6546,7 @@
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -6273,7 +6570,7 @@
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -6297,7 +6594,7 @@
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -6321,7 +6618,7 @@
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -6345,7 +6642,7 @@
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -6369,7 +6666,7 @@
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -6393,7 +6690,7 @@
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -6417,7 +6714,7 @@
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -6441,7 +6738,7 @@
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -6465,7 +6762,7 @@
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -6489,7 +6786,7 @@
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -6513,7 +6810,7 @@
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -6537,7 +6834,7 @@
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -6561,7 +6858,7 @@
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -6585,7 +6882,7 @@
       <c r="U23" s="5"/>
       <c r="V23" s="5"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -6609,7 +6906,7 @@
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -6633,7 +6930,7 @@
       <c r="U25" s="5"/>
       <c r="V25" s="5"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -6657,7 +6954,7 @@
       <c r="U26" s="5"/>
       <c r="V26" s="5"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -6681,7 +6978,7 @@
       <c r="U27" s="5"/>
       <c r="V27" s="5"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -6705,7 +7002,7 @@
       <c r="U28" s="5"/>
       <c r="V28" s="5"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -6729,7 +7026,7 @@
       <c r="U29" s="5"/>
       <c r="V29" s="5"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -6753,7 +7050,7 @@
       <c r="U30" s="5"/>
       <c r="V30" s="5"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -6777,7 +7074,7 @@
       <c r="U31" s="5"/>
       <c r="V31" s="5"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -6801,7 +7098,7 @@
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -6825,7 +7122,7 @@
       <c r="U33" s="5"/>
       <c r="V33" s="5"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -6849,7 +7146,7 @@
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -6873,7 +7170,7 @@
       <c r="U35" s="5"/>
       <c r="V35" s="5"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -6897,7 +7194,7 @@
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -6921,7 +7218,7 @@
       <c r="U37" s="5"/>
       <c r="V37" s="5"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -6945,7 +7242,7 @@
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -6969,7 +7266,7 @@
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -6993,7 +7290,7 @@
       <c r="U40" s="5"/>
       <c r="V40" s="5"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -7017,7 +7314,7 @@
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -7041,7 +7338,7 @@
       <c r="U42" s="5"/>
       <c r="V42" s="5"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -7065,7 +7362,7 @@
       <c r="U43" s="5"/>
       <c r="V43" s="5"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -7089,7 +7386,7 @@
       <c r="U44" s="5"/>
       <c r="V44" s="5"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -7113,7 +7410,7 @@
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -7137,7 +7434,7 @@
       <c r="U46" s="5"/>
       <c r="V46" s="5"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -7161,7 +7458,7 @@
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -7185,7 +7482,7 @@
       <c r="U48" s="5"/>
       <c r="V48" s="5"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -7209,7 +7506,7 @@
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -7233,7 +7530,7 @@
       <c r="U50" s="5"/>
       <c r="V50" s="5"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -7257,7 +7554,7 @@
       <c r="U51" s="5"/>
       <c r="V51" s="5"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -7281,7 +7578,7 @@
       <c r="U52" s="5"/>
       <c r="V52" s="5"/>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -7305,7 +7602,7 @@
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -7329,7 +7626,7 @@
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -7353,7 +7650,7 @@
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -7377,7 +7674,7 @@
       <c r="U56" s="5"/>
       <c r="V56" s="5"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -7401,7 +7698,7 @@
       <c r="U57" s="5"/>
       <c r="V57" s="5"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -7425,7 +7722,7 @@
       <c r="U58" s="5"/>
       <c r="V58" s="5"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -7449,7 +7746,7 @@
       <c r="U59" s="5"/>
       <c r="V59" s="5"/>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -7473,7 +7770,7 @@
       <c r="U60" s="5"/>
       <c r="V60" s="5"/>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -7497,7 +7794,7 @@
       <c r="U61" s="5"/>
       <c r="V61" s="5"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -7521,7 +7818,7 @@
       <c r="U62" s="5"/>
       <c r="V62" s="5"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -7545,7 +7842,7 @@
       <c r="U63" s="5"/>
       <c r="V63" s="5"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -7569,7 +7866,7 @@
       <c r="U64" s="5"/>
       <c r="V64" s="5"/>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -7593,7 +7890,7 @@
       <c r="U65" s="5"/>
       <c r="V65" s="5"/>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -7617,7 +7914,7 @@
       <c r="U66" s="5"/>
       <c r="V66" s="5"/>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -7641,7 +7938,7 @@
       <c r="U67" s="5"/>
       <c r="V67" s="5"/>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -7665,7 +7962,7 @@
       <c r="U68" s="5"/>
       <c r="V68" s="5"/>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -7689,7 +7986,7 @@
       <c r="U69" s="5"/>
       <c r="V69" s="5"/>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -7713,7 +8010,7 @@
       <c r="U70" s="5"/>
       <c r="V70" s="5"/>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -7737,7 +8034,7 @@
       <c r="U71" s="5"/>
       <c r="V71" s="5"/>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -7761,7 +8058,7 @@
       <c r="U72" s="5"/>
       <c r="V72" s="5"/>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -7785,7 +8082,7 @@
       <c r="U73" s="5"/>
       <c r="V73" s="5"/>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -7809,7 +8106,7 @@
       <c r="U74" s="5"/>
       <c r="V74" s="5"/>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -7833,7 +8130,7 @@
       <c r="U75" s="5"/>
       <c r="V75" s="5"/>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -7857,7 +8154,7 @@
       <c r="U76" s="5"/>
       <c r="V76" s="5"/>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -7881,7 +8178,7 @@
       <c r="U77" s="5"/>
       <c r="V77" s="5"/>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -7905,7 +8202,7 @@
       <c r="U78" s="5"/>
       <c r="V78" s="5"/>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -7929,7 +8226,7 @@
       <c r="U79" s="5"/>
       <c r="V79" s="5"/>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -7953,7 +8250,7 @@
       <c r="U80" s="5"/>
       <c r="V80" s="5"/>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -7977,7 +8274,7 @@
       <c r="U81" s="5"/>
       <c r="V81" s="5"/>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -8001,7 +8298,7 @@
       <c r="U82" s="5"/>
       <c r="V82" s="5"/>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -8025,7 +8322,7 @@
       <c r="U83" s="5"/>
       <c r="V83" s="5"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -8049,7 +8346,7 @@
       <c r="U84" s="5"/>
       <c r="V84" s="5"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -8073,7 +8370,7 @@
       <c r="U85" s="5"/>
       <c r="V85" s="5"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -8097,7 +8394,7 @@
       <c r="U86" s="5"/>
       <c r="V86" s="5"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -8121,7 +8418,7 @@
       <c r="U87" s="5"/>
       <c r="V87" s="5"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -8145,7 +8442,7 @@
       <c r="U88" s="5"/>
       <c r="V88" s="5"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -8169,7 +8466,7 @@
       <c r="U89" s="5"/>
       <c r="V89" s="5"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -8193,7 +8490,7 @@
       <c r="U90" s="5"/>
       <c r="V90" s="5"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -8217,7 +8514,7 @@
       <c r="U91" s="5"/>
       <c r="V91" s="5"/>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -8241,7 +8538,7 @@
       <c r="U92" s="5"/>
       <c r="V92" s="5"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -8265,7 +8562,7 @@
       <c r="U93" s="5"/>
       <c r="V93" s="5"/>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -8289,7 +8586,7 @@
       <c r="U94" s="5"/>
       <c r="V94" s="5"/>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -8313,7 +8610,7 @@
       <c r="U95" s="5"/>
       <c r="V95" s="5"/>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -8337,7 +8634,7 @@
       <c r="U96" s="5"/>
       <c r="V96" s="5"/>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -8361,7 +8658,7 @@
       <c r="U97" s="5"/>
       <c r="V97" s="5"/>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -8385,7 +8682,7 @@
       <c r="U98" s="5"/>
       <c r="V98" s="5"/>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -8409,7 +8706,7 @@
       <c r="U99" s="5"/>
       <c r="V99" s="5"/>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -8433,7 +8730,7 @@
       <c r="U100" s="5"/>
       <c r="V100" s="5"/>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -8457,7 +8754,7 @@
       <c r="U101" s="5"/>
       <c r="V101" s="5"/>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -8481,7 +8778,7 @@
       <c r="U102" s="5"/>
       <c r="V102" s="5"/>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -8505,7 +8802,7 @@
       <c r="U103" s="5"/>
       <c r="V103" s="5"/>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -8529,7 +8826,7 @@
       <c r="U104" s="5"/>
       <c r="V104" s="5"/>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -8553,7 +8850,7 @@
       <c r="U105" s="5"/>
       <c r="V105" s="5"/>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -8577,7 +8874,7 @@
       <c r="U106" s="5"/>
       <c r="V106" s="5"/>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -8601,7 +8898,7 @@
       <c r="U107" s="5"/>
       <c r="V107" s="5"/>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -8625,7 +8922,7 @@
       <c r="U108" s="5"/>
       <c r="V108" s="5"/>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -8649,7 +8946,7 @@
       <c r="U109" s="5"/>
       <c r="V109" s="5"/>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -8673,7 +8970,7 @@
       <c r="U110" s="5"/>
       <c r="V110" s="5"/>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -8697,7 +8994,7 @@
       <c r="U111" s="5"/>
       <c r="V111" s="5"/>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -8721,7 +9018,7 @@
       <c r="U112" s="5"/>
       <c r="V112" s="5"/>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -8745,7 +9042,7 @@
       <c r="U113" s="5"/>
       <c r="V113" s="5"/>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -8769,7 +9066,7 @@
       <c r="U114" s="5"/>
       <c r="V114" s="5"/>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -8793,7 +9090,7 @@
       <c r="U115" s="5"/>
       <c r="V115" s="5"/>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -8817,7 +9114,7 @@
       <c r="U116" s="5"/>
       <c r="V116" s="5"/>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -8841,7 +9138,7 @@
       <c r="U117" s="5"/>
       <c r="V117" s="5"/>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -8865,7 +9162,7 @@
       <c r="U118" s="5"/>
       <c r="V118" s="5"/>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -8889,7 +9186,7 @@
       <c r="U119" s="5"/>
       <c r="V119" s="5"/>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -8913,7 +9210,7 @@
       <c r="U120" s="5"/>
       <c r="V120" s="5"/>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -8937,7 +9234,7 @@
       <c r="U121" s="5"/>
       <c r="V121" s="5"/>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -8961,7 +9258,7 @@
       <c r="U122" s="5"/>
       <c r="V122" s="5"/>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -8985,7 +9282,7 @@
       <c r="U123" s="5"/>
       <c r="V123" s="5"/>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -9009,7 +9306,7 @@
       <c r="U124" s="5"/>
       <c r="V124" s="5"/>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -9033,7 +9330,7 @@
       <c r="U125" s="5"/>
       <c r="V125" s="5"/>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -9057,7 +9354,7 @@
       <c r="U126" s="5"/>
       <c r="V126" s="5"/>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -9081,7 +9378,7 @@
       <c r="U127" s="5"/>
       <c r="V127" s="5"/>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -9105,7 +9402,7 @@
       <c r="U128" s="5"/>
       <c r="V128" s="5"/>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -9129,7 +9426,7 @@
       <c r="U129" s="5"/>
       <c r="V129" s="5"/>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -9153,7 +9450,7 @@
       <c r="U130" s="5"/>
       <c r="V130" s="5"/>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -9177,7 +9474,7 @@
       <c r="U131" s="5"/>
       <c r="V131" s="5"/>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -9201,7 +9498,7 @@
       <c r="U132" s="5"/>
       <c r="V132" s="5"/>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -9225,7 +9522,7 @@
       <c r="U133" s="5"/>
       <c r="V133" s="5"/>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -9249,7 +9546,7 @@
       <c r="U134" s="5"/>
       <c r="V134" s="5"/>
     </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -9273,7 +9570,7 @@
       <c r="U135" s="5"/>
       <c r="V135" s="5"/>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -9297,7 +9594,7 @@
       <c r="U136" s="5"/>
       <c r="V136" s="5"/>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -9321,7 +9618,7 @@
       <c r="U137" s="5"/>
       <c r="V137" s="5"/>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -9345,7 +9642,7 @@
       <c r="U138" s="5"/>
       <c r="V138" s="5"/>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -9369,7 +9666,7 @@
       <c r="U139" s="5"/>
       <c r="V139" s="5"/>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -9393,7 +9690,7 @@
       <c r="U140" s="5"/>
       <c r="V140" s="5"/>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -9417,7 +9714,7 @@
       <c r="U141" s="5"/>
       <c r="V141" s="5"/>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -9441,7 +9738,7 @@
       <c r="U142" s="5"/>
       <c r="V142" s="5"/>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -9465,7 +9762,7 @@
       <c r="U143" s="5"/>
       <c r="V143" s="5"/>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -9489,7 +9786,7 @@
       <c r="U144" s="5"/>
       <c r="V144" s="5"/>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -9513,7 +9810,7 @@
       <c r="U145" s="5"/>
       <c r="V145" s="5"/>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -9537,7 +9834,7 @@
       <c r="U146" s="5"/>
       <c r="V146" s="5"/>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -9561,7 +9858,7 @@
       <c r="U147" s="5"/>
       <c r="V147" s="5"/>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -9585,7 +9882,7 @@
       <c r="U148" s="5"/>
       <c r="V148" s="5"/>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -9609,7 +9906,7 @@
       <c r="U149" s="5"/>
       <c r="V149" s="5"/>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -9633,7 +9930,7 @@
       <c r="U150" s="5"/>
       <c r="V150" s="5"/>
     </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -9657,7 +9954,7 @@
       <c r="U151" s="5"/>
       <c r="V151" s="5"/>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -9681,7 +9978,7 @@
       <c r="U152" s="5"/>
       <c r="V152" s="5"/>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -9705,7 +10002,7 @@
       <c r="U153" s="5"/>
       <c r="V153" s="5"/>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -9729,7 +10026,7 @@
       <c r="U154" s="5"/>
       <c r="V154" s="5"/>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -9753,7 +10050,7 @@
       <c r="U155" s="5"/>
       <c r="V155" s="5"/>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -9777,7 +10074,7 @@
       <c r="U156" s="5"/>
       <c r="V156" s="5"/>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -9801,7 +10098,7 @@
       <c r="U157" s="5"/>
       <c r="V157" s="5"/>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -9825,7 +10122,7 @@
       <c r="U158" s="5"/>
       <c r="V158" s="5"/>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -9849,7 +10146,7 @@
       <c r="U159" s="5"/>
       <c r="V159" s="5"/>
     </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -9873,7 +10170,7 @@
       <c r="U160" s="5"/>
       <c r="V160" s="5"/>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -9897,7 +10194,7 @@
       <c r="U161" s="5"/>
       <c r="V161" s="5"/>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -9921,7 +10218,7 @@
       <c r="U162" s="5"/>
       <c r="V162" s="5"/>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -9945,7 +10242,7 @@
       <c r="U163" s="5"/>
       <c r="V163" s="5"/>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -9969,7 +10266,7 @@
       <c r="U164" s="5"/>
       <c r="V164" s="5"/>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -9993,7 +10290,7 @@
       <c r="U165" s="5"/>
       <c r="V165" s="5"/>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -10017,7 +10314,7 @@
       <c r="U166" s="5"/>
       <c r="V166" s="5"/>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -10041,7 +10338,7 @@
       <c r="U167" s="5"/>
       <c r="V167" s="5"/>
     </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -10065,7 +10362,7 @@
       <c r="U168" s="5"/>
       <c r="V168" s="5"/>
     </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -10089,7 +10386,7 @@
       <c r="U169" s="5"/>
       <c r="V169" s="5"/>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -10113,7 +10410,7 @@
       <c r="U170" s="5"/>
       <c r="V170" s="5"/>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -10137,7 +10434,7 @@
       <c r="U171" s="5"/>
       <c r="V171" s="5"/>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -10161,7 +10458,7 @@
       <c r="U172" s="5"/>
       <c r="V172" s="5"/>
     </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -10185,7 +10482,7 @@
       <c r="U173" s="5"/>
       <c r="V173" s="5"/>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -10209,7 +10506,7 @@
       <c r="U174" s="5"/>
       <c r="V174" s="5"/>
     </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -10233,7 +10530,7 @@
       <c r="U175" s="5"/>
       <c r="V175" s="5"/>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -10257,7 +10554,7 @@
       <c r="U176" s="5"/>
       <c r="V176" s="5"/>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -10281,7 +10578,7 @@
       <c r="U177" s="5"/>
       <c r="V177" s="5"/>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -10305,7 +10602,7 @@
       <c r="U178" s="5"/>
       <c r="V178" s="5"/>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -10329,7 +10626,7 @@
       <c r="U179" s="5"/>
       <c r="V179" s="5"/>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -10353,7 +10650,7 @@
       <c r="U180" s="5"/>
       <c r="V180" s="5"/>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -10377,7 +10674,7 @@
       <c r="U181" s="5"/>
       <c r="V181" s="5"/>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -10401,7 +10698,7 @@
       <c r="U182" s="5"/>
       <c r="V182" s="5"/>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -10425,7 +10722,7 @@
       <c r="U183" s="5"/>
       <c r="V183" s="5"/>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -10449,7 +10746,7 @@
       <c r="U184" s="5"/>
       <c r="V184" s="5"/>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -10473,7 +10770,7 @@
       <c r="U185" s="5"/>
       <c r="V185" s="5"/>
     </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -10497,7 +10794,7 @@
       <c r="U186" s="5"/>
       <c r="V186" s="5"/>
     </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -10521,7 +10818,7 @@
       <c r="U187" s="5"/>
       <c r="V187" s="5"/>
     </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -10545,7 +10842,7 @@
       <c r="U188" s="5"/>
       <c r="V188" s="5"/>
     </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -10569,7 +10866,7 @@
       <c r="U189" s="5"/>
       <c r="V189" s="5"/>
     </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -10593,7 +10890,7 @@
       <c r="U190" s="5"/>
       <c r="V190" s="5"/>
     </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -10617,7 +10914,7 @@
       <c r="U191" s="5"/>
       <c r="V191" s="5"/>
     </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -10641,7 +10938,7 @@
       <c r="U192" s="5"/>
       <c r="V192" s="5"/>
     </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -10665,7 +10962,7 @@
       <c r="U193" s="5"/>
       <c r="V193" s="5"/>
     </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -10689,7 +10986,7 @@
       <c r="U194" s="5"/>
       <c r="V194" s="5"/>
     </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -10713,7 +11010,7 @@
       <c r="U195" s="5"/>
       <c r="V195" s="5"/>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -10737,7 +11034,7 @@
       <c r="U196" s="5"/>
       <c r="V196" s="5"/>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -10761,7 +11058,7 @@
       <c r="U197" s="5"/>
       <c r="V197" s="5"/>
     </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -10785,7 +11082,7 @@
       <c r="U198" s="5"/>
       <c r="V198" s="5"/>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -10809,7 +11106,7 @@
       <c r="U199" s="5"/>
       <c r="V199" s="5"/>
     </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -10848,17 +11145,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:T200"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -10874,7 +11171,7 @@
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>54</v>
       </c>
@@ -10908,7 +11205,7 @@
       <c r="S2" s="5"/>
       <c r="T2" s="5"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>60</v>
       </c>
@@ -10924,10 +11221,10 @@
       <c r="E3" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -10942,7 +11239,7 @@
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>64</v>
       </c>
@@ -10978,7 +11275,7 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -11000,7 +11297,7 @@
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -11022,7 +11319,7 @@
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -11044,7 +11341,7 @@
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -11066,7 +11363,7 @@
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -11088,7 +11385,7 @@
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -11110,7 +11407,7 @@
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -11132,7 +11429,7 @@
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -11154,7 +11451,7 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -11176,7 +11473,7 @@
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -11198,7 +11495,7 @@
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -11220,7 +11517,7 @@
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -11242,7 +11539,7 @@
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -11264,7 +11561,7 @@
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -11286,7 +11583,7 @@
       <c r="S18" s="5"/>
       <c r="T18" s="5"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -11308,7 +11605,7 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -11330,7 +11627,7 @@
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -11352,7 +11649,7 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -11374,7 +11671,7 @@
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -11396,7 +11693,7 @@
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -11418,7 +11715,7 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -11440,7 +11737,7 @@
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -11462,7 +11759,7 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -11484,7 +11781,7 @@
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -11506,7 +11803,7 @@
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -11528,7 +11825,7 @@
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -11550,7 +11847,7 @@
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -11572,7 +11869,7 @@
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -11594,7 +11891,7 @@
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -11616,7 +11913,7 @@
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -11638,7 +11935,7 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -11660,7 +11957,7 @@
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -11682,7 +11979,7 @@
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -11704,7 +12001,7 @@
       <c r="S37" s="5"/>
       <c r="T37" s="5"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -11726,7 +12023,7 @@
       <c r="S38" s="5"/>
       <c r="T38" s="5"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -11748,7 +12045,7 @@
       <c r="S39" s="5"/>
       <c r="T39" s="5"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -11770,7 +12067,7 @@
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -11792,7 +12089,7 @@
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -11814,7 +12111,7 @@
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -11836,7 +12133,7 @@
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -11858,7 +12155,7 @@
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -11880,7 +12177,7 @@
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -11902,7 +12199,7 @@
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -11924,7 +12221,7 @@
       <c r="S47" s="5"/>
       <c r="T47" s="5"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -11946,7 +12243,7 @@
       <c r="S48" s="5"/>
       <c r="T48" s="5"/>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -11968,7 +12265,7 @@
       <c r="S49" s="5"/>
       <c r="T49" s="5"/>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -11990,7 +12287,7 @@
       <c r="S50" s="5"/>
       <c r="T50" s="5"/>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -12012,7 +12309,7 @@
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -12034,7 +12331,7 @@
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -12056,7 +12353,7 @@
       <c r="S53" s="5"/>
       <c r="T53" s="5"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -12078,7 +12375,7 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -12100,7 +12397,7 @@
       <c r="S55" s="5"/>
       <c r="T55" s="5"/>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -12122,7 +12419,7 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -12144,7 +12441,7 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -12166,7 +12463,7 @@
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -12188,7 +12485,7 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -12210,7 +12507,7 @@
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -12232,7 +12529,7 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -12254,7 +12551,7 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -12276,7 +12573,7 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -12298,7 +12595,7 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -12320,7 +12617,7 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -12342,7 +12639,7 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -12364,7 +12661,7 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -12386,7 +12683,7 @@
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -12408,7 +12705,7 @@
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -12430,7 +12727,7 @@
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -12452,7 +12749,7 @@
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -12474,7 +12771,7 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -12496,7 +12793,7 @@
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -12518,7 +12815,7 @@
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -12540,7 +12837,7 @@
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -12562,7 +12859,7 @@
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -12584,7 +12881,7 @@
       <c r="S77" s="5"/>
       <c r="T77" s="5"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -12606,7 +12903,7 @@
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -12628,7 +12925,7 @@
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -12650,7 +12947,7 @@
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -12672,7 +12969,7 @@
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -12694,7 +12991,7 @@
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -12716,7 +13013,7 @@
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -12738,7 +13035,7 @@
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -12760,7 +13057,7 @@
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -12782,7 +13079,7 @@
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -12804,7 +13101,7 @@
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -12826,7 +13123,7 @@
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -12848,7 +13145,7 @@
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -12870,7 +13167,7 @@
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -12892,7 +13189,7 @@
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -12914,7 +13211,7 @@
       <c r="S92" s="5"/>
       <c r="T92" s="5"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -12936,7 +13233,7 @@
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -12958,7 +13255,7 @@
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -12980,7 +13277,7 @@
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -13002,7 +13299,7 @@
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -13024,7 +13321,7 @@
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -13046,7 +13343,7 @@
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -13068,7 +13365,7 @@
       <c r="S99" s="5"/>
       <c r="T99" s="5"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -13090,7 +13387,7 @@
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -13112,7 +13409,7 @@
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -13134,7 +13431,7 @@
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -13156,7 +13453,7 @@
       <c r="S103" s="5"/>
       <c r="T103" s="5"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -13178,7 +13475,7 @@
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -13200,7 +13497,7 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -13222,7 +13519,7 @@
       <c r="S106" s="5"/>
       <c r="T106" s="5"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -13244,7 +13541,7 @@
       <c r="S107" s="5"/>
       <c r="T107" s="5"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -13266,7 +13563,7 @@
       <c r="S108" s="5"/>
       <c r="T108" s="5"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -13288,7 +13585,7 @@
       <c r="S109" s="5"/>
       <c r="T109" s="5"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -13310,7 +13607,7 @@
       <c r="S110" s="5"/>
       <c r="T110" s="5"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -13332,7 +13629,7 @@
       <c r="S111" s="5"/>
       <c r="T111" s="5"/>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -13354,7 +13651,7 @@
       <c r="S112" s="5"/>
       <c r="T112" s="5"/>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -13376,7 +13673,7 @@
       <c r="S113" s="5"/>
       <c r="T113" s="5"/>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -13398,7 +13695,7 @@
       <c r="S114" s="5"/>
       <c r="T114" s="5"/>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -13420,7 +13717,7 @@
       <c r="S115" s="5"/>
       <c r="T115" s="5"/>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -13442,7 +13739,7 @@
       <c r="S116" s="5"/>
       <c r="T116" s="5"/>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -13464,7 +13761,7 @@
       <c r="S117" s="5"/>
       <c r="T117" s="5"/>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -13486,7 +13783,7 @@
       <c r="S118" s="5"/>
       <c r="T118" s="5"/>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -13508,7 +13805,7 @@
       <c r="S119" s="5"/>
       <c r="T119" s="5"/>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -13530,7 +13827,7 @@
       <c r="S120" s="5"/>
       <c r="T120" s="5"/>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -13552,7 +13849,7 @@
       <c r="S121" s="5"/>
       <c r="T121" s="5"/>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -13574,7 +13871,7 @@
       <c r="S122" s="5"/>
       <c r="T122" s="5"/>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -13596,7 +13893,7 @@
       <c r="S123" s="5"/>
       <c r="T123" s="5"/>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -13618,7 +13915,7 @@
       <c r="S124" s="5"/>
       <c r="T124" s="5"/>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -13640,7 +13937,7 @@
       <c r="S125" s="5"/>
       <c r="T125" s="5"/>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -13662,7 +13959,7 @@
       <c r="S126" s="5"/>
       <c r="T126" s="5"/>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -13684,7 +13981,7 @@
       <c r="S127" s="5"/>
       <c r="T127" s="5"/>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -13706,7 +14003,7 @@
       <c r="S128" s="5"/>
       <c r="T128" s="5"/>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -13728,7 +14025,7 @@
       <c r="S129" s="5"/>
       <c r="T129" s="5"/>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -13750,7 +14047,7 @@
       <c r="S130" s="5"/>
       <c r="T130" s="5"/>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -13772,7 +14069,7 @@
       <c r="S131" s="5"/>
       <c r="T131" s="5"/>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -13794,7 +14091,7 @@
       <c r="S132" s="5"/>
       <c r="T132" s="5"/>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -13816,7 +14113,7 @@
       <c r="S133" s="5"/>
       <c r="T133" s="5"/>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -13838,7 +14135,7 @@
       <c r="S134" s="5"/>
       <c r="T134" s="5"/>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -13860,7 +14157,7 @@
       <c r="S135" s="5"/>
       <c r="T135" s="5"/>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -13882,7 +14179,7 @@
       <c r="S136" s="5"/>
       <c r="T136" s="5"/>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -13904,7 +14201,7 @@
       <c r="S137" s="5"/>
       <c r="T137" s="5"/>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -13926,7 +14223,7 @@
       <c r="S138" s="5"/>
       <c r="T138" s="5"/>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -13948,7 +14245,7 @@
       <c r="S139" s="5"/>
       <c r="T139" s="5"/>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -13970,7 +14267,7 @@
       <c r="S140" s="5"/>
       <c r="T140" s="5"/>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -13992,7 +14289,7 @@
       <c r="S141" s="5"/>
       <c r="T141" s="5"/>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -14014,7 +14311,7 @@
       <c r="S142" s="5"/>
       <c r="T142" s="5"/>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -14036,7 +14333,7 @@
       <c r="S143" s="5"/>
       <c r="T143" s="5"/>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -14058,7 +14355,7 @@
       <c r="S144" s="5"/>
       <c r="T144" s="5"/>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -14080,7 +14377,7 @@
       <c r="S145" s="5"/>
       <c r="T145" s="5"/>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -14102,7 +14399,7 @@
       <c r="S146" s="5"/>
       <c r="T146" s="5"/>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -14124,7 +14421,7 @@
       <c r="S147" s="5"/>
       <c r="T147" s="5"/>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -14146,7 +14443,7 @@
       <c r="S148" s="5"/>
       <c r="T148" s="5"/>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -14168,7 +14465,7 @@
       <c r="S149" s="5"/>
       <c r="T149" s="5"/>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -14190,7 +14487,7 @@
       <c r="S150" s="5"/>
       <c r="T150" s="5"/>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -14212,7 +14509,7 @@
       <c r="S151" s="5"/>
       <c r="T151" s="5"/>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -14234,7 +14531,7 @@
       <c r="S152" s="5"/>
       <c r="T152" s="5"/>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -14256,7 +14553,7 @@
       <c r="S153" s="5"/>
       <c r="T153" s="5"/>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -14278,7 +14575,7 @@
       <c r="S154" s="5"/>
       <c r="T154" s="5"/>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -14300,7 +14597,7 @@
       <c r="S155" s="5"/>
       <c r="T155" s="5"/>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -14322,7 +14619,7 @@
       <c r="S156" s="5"/>
       <c r="T156" s="5"/>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -14344,7 +14641,7 @@
       <c r="S157" s="5"/>
       <c r="T157" s="5"/>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -14366,7 +14663,7 @@
       <c r="S158" s="5"/>
       <c r="T158" s="5"/>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
@@ -14388,7 +14685,7 @@
       <c r="S159" s="5"/>
       <c r="T159" s="5"/>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
@@ -14410,7 +14707,7 @@
       <c r="S160" s="5"/>
       <c r="T160" s="5"/>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
@@ -14432,7 +14729,7 @@
       <c r="S161" s="5"/>
       <c r="T161" s="5"/>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
@@ -14454,7 +14751,7 @@
       <c r="S162" s="5"/>
       <c r="T162" s="5"/>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
@@ -14476,7 +14773,7 @@
       <c r="S163" s="5"/>
       <c r="T163" s="5"/>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
@@ -14498,7 +14795,7 @@
       <c r="S164" s="5"/>
       <c r="T164" s="5"/>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
@@ -14520,7 +14817,7 @@
       <c r="S165" s="5"/>
       <c r="T165" s="5"/>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
@@ -14542,7 +14839,7 @@
       <c r="S166" s="5"/>
       <c r="T166" s="5"/>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
@@ -14564,7 +14861,7 @@
       <c r="S167" s="5"/>
       <c r="T167" s="5"/>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
@@ -14586,7 +14883,7 @@
       <c r="S168" s="5"/>
       <c r="T168" s="5"/>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
@@ -14608,7 +14905,7 @@
       <c r="S169" s="5"/>
       <c r="T169" s="5"/>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
@@ -14630,7 +14927,7 @@
       <c r="S170" s="5"/>
       <c r="T170" s="5"/>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
@@ -14652,7 +14949,7 @@
       <c r="S171" s="5"/>
       <c r="T171" s="5"/>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
@@ -14674,7 +14971,7 @@
       <c r="S172" s="5"/>
       <c r="T172" s="5"/>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
@@ -14696,7 +14993,7 @@
       <c r="S173" s="5"/>
       <c r="T173" s="5"/>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
@@ -14718,7 +15015,7 @@
       <c r="S174" s="5"/>
       <c r="T174" s="5"/>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
@@ -14740,7 +15037,7 @@
       <c r="S175" s="5"/>
       <c r="T175" s="5"/>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
@@ -14762,7 +15059,7 @@
       <c r="S176" s="5"/>
       <c r="T176" s="5"/>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
@@ -14784,7 +15081,7 @@
       <c r="S177" s="5"/>
       <c r="T177" s="5"/>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
@@ -14806,7 +15103,7 @@
       <c r="S178" s="5"/>
       <c r="T178" s="5"/>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
@@ -14828,7 +15125,7 @@
       <c r="S179" s="5"/>
       <c r="T179" s="5"/>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
@@ -14850,7 +15147,7 @@
       <c r="S180" s="5"/>
       <c r="T180" s="5"/>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -14872,7 +15169,7 @@
       <c r="S181" s="5"/>
       <c r="T181" s="5"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
@@ -14894,7 +15191,7 @@
       <c r="S182" s="5"/>
       <c r="T182" s="5"/>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
@@ -14916,7 +15213,7 @@
       <c r="S183" s="5"/>
       <c r="T183" s="5"/>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -14938,7 +15235,7 @@
       <c r="S184" s="5"/>
       <c r="T184" s="5"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -14960,7 +15257,7 @@
       <c r="S185" s="5"/>
       <c r="T185" s="5"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -14982,7 +15279,7 @@
       <c r="S186" s="5"/>
       <c r="T186" s="5"/>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -15004,7 +15301,7 @@
       <c r="S187" s="5"/>
       <c r="T187" s="5"/>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -15026,7 +15323,7 @@
       <c r="S188" s="5"/>
       <c r="T188" s="5"/>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -15048,7 +15345,7 @@
       <c r="S189" s="5"/>
       <c r="T189" s="5"/>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -15070,7 +15367,7 @@
       <c r="S190" s="5"/>
       <c r="T190" s="5"/>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -15092,7 +15389,7 @@
       <c r="S191" s="5"/>
       <c r="T191" s="5"/>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -15114,7 +15411,7 @@
       <c r="S192" s="5"/>
       <c r="T192" s="5"/>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -15136,7 +15433,7 @@
       <c r="S193" s="5"/>
       <c r="T193" s="5"/>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -15158,7 +15455,7 @@
       <c r="S194" s="5"/>
       <c r="T194" s="5"/>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -15180,7 +15477,7 @@
       <c r="S195" s="5"/>
       <c r="T195" s="5"/>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -15202,7 +15499,7 @@
       <c r="S196" s="5"/>
       <c r="T196" s="5"/>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -15224,7 +15521,7 @@
       <c r="S197" s="5"/>
       <c r="T197" s="5"/>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -15246,7 +15543,7 @@
       <c r="S198" s="5"/>
       <c r="T198" s="5"/>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -15268,7 +15565,7 @@
       <c r="S199" s="5"/>
       <c r="T199" s="5"/>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -15301,22 +15598,705 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09443683-AC20-492E-842F-172C5AB5F4BF}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="17">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="17">
+        <v>3</v>
+      </c>
+      <c r="D4" s="17">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="17">
+        <v>0</v>
+      </c>
+      <c r="D5" s="17">
+        <v>2</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="G3:G5"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F06CB3E-FA71-45E5-84E4-60FF3174EA5A}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="17">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="22"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="17">
+        <v>3</v>
+      </c>
+      <c r="D5" s="17">
+        <v>1</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="G3:G5"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25809669-A641-4E0E-A5D3-B34C72805BAE}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="27"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="24">
+        <v>0</v>
+      </c>
+      <c r="C3" s="24">
+        <v>0</v>
+      </c>
+      <c r="D3" s="24">
+        <v>1</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="29"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="29"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" s="29"/>
+    </row>
+    <row r="7" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="24">
+        <v>0</v>
+      </c>
+      <c r="C7" s="24">
+        <v>0</v>
+      </c>
+      <c r="D7" s="24">
+        <v>1</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="G3:G7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A8FF61-EA26-4768-A8B8-4AA75A1DFD85}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="27"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="24">
+        <v>1</v>
+      </c>
+      <c r="D4" s="24">
+        <v>1</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="34"/>
+    </row>
+    <row r="5" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="24">
+        <v>4</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="34"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="24">
+        <v>2</v>
+      </c>
+      <c r="D6" s="24">
+        <v>1</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="G6" s="34"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="24">
+        <v>3</v>
+      </c>
+      <c r="D7" s="24">
+        <v>2</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="G3:G7"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C670B6-AE02-45AD-9D58-D1C95B30B80B}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="24">
+        <v>4</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="24">
+        <v>0</v>
+      </c>
+      <c r="C5" s="24">
+        <v>2</v>
+      </c>
+      <c r="D5" s="24">
+        <v>1</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="F2:H2"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9AEB45-C00A-4E35-82A0-F634394E5572}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -15337,7 +16317,7 @@
       </c>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -15357,7 +16337,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -15377,7 +16357,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -15397,7 +16377,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -15417,7 +16397,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>95</v>
       </c>
@@ -15437,7 +16417,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -15457,7 +16437,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>101</v>
       </c>
@@ -15477,7 +16457,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>107</v>
       </c>
@@ -15497,7 +16477,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -15517,7 +16497,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>112</v>
       </c>
@@ -15537,7 +16517,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>114</v>
       </c>
